--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI13"/>
+  <dimension ref="A1:BI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46106.85416666666</v>
+        <v>46106.83333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46106.875</v>
+        <v>46106.85416666666</v>
       </c>
     </row>
     <row r="12">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.875</v>
       </c>
     </row>
     <row r="13">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,6 +3103,203 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
+        <v>46106.91666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" s="3" t="n">
         <v>46106.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -797,116 +797,116 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -994,116 +994,116 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI14"/>
+  <dimension ref="A1:BI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,25 +1204,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1231,25 +1231,25 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1258,16 +1258,16 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46106.72916666666</v>
+        <v>46106.57291666666</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46106.72916666666</v>
+        <v>46106.66666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46106.83333333334</v>
+        <v>46106.72916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46106.83333333334</v>
+        <v>46106.72916666666</v>
       </c>
     </row>
     <row r="9">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46106.85416666666</v>
+        <v>46106.83333333334</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46106.875</v>
+        <v>46106.85416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.875</v>
       </c>
     </row>
     <row r="14">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,6 +3300,203 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
+        <v>46106.91666666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
         <v>46106.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.84</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="U3" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Y3" t="n">
         <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.55</v>
+        <v>5.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
         <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.22</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC3" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1010,19 +1010,19 @@
         <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="X3" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
         <v>1.4</v>
@@ -1037,40 +1037,40 @@
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
         <v>5.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.36</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,13 +1115,13 @@
         <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="BD3" t="n">
         <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
         <v>1.17</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
@@ -1019,7 +1019,7 @@
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>2.97</v>
+        <v>2.76</v>
       </c>
       <c r="X3" t="n">
         <v>2.53</v>
@@ -1043,7 +1043,7 @@
         <v>3.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
         <v>1.97</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="S3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
         <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3174,70 +3174,70 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
@@ -813,10 +813,10 @@
         <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>5.6</v>
+        <v>5.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
@@ -849,7 +849,7 @@
         <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
         <v>2.78</v>
@@ -864,7 +864,7 @@
         <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
         <v>1.88</v>
@@ -918,7 +918,7 @@
         <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
         <v>3.8</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="S2" t="n">
         <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>5.88</v>
+        <v>5.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
@@ -828,22 +828,22 @@
         <v>2.53</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AE2" t="n">
         <v>1.92</v>
@@ -852,28 +852,28 @@
         <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -924,7 +924,7 @@
         <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BF2" t="n">
         <v>1.17</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="R11" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2977,70 +2977,70 @@
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3174,70 +3174,70 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="X14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.06</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AM14" t="n">
         <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BC14" t="n">
         <v>2.29</v>
@@ -3288,10 +3288,10 @@
         <v>3.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3371,70 +3371,70 @@
         <v>3.06</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
         <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="R2" t="n">
-        <v>6.4</v>
+        <v>5.76</v>
       </c>
       <c r="S2" t="n">
         <v>1.85</v>
@@ -816,16 +816,16 @@
         <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
         <v>1.48</v>
@@ -855,7 +855,7 @@
         <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
         <v>5</v>
@@ -924,7 +924,7 @@
         <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BF2" t="n">
         <v>1.17</v>
@@ -2595,19 +2595,19 @@
         <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="X11" t="n">
         <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
         <v>1.01</v>
@@ -2616,13 +2616,13 @@
         <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
         <v>2.5</v>
@@ -2640,13 +2640,13 @@
         <v>1.73</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BC11" t="n">
         <v>1.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BE11" t="n">
         <v>1.85</v>
@@ -3007,16 +3007,16 @@
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
         <v>2.9</v>
@@ -3028,7 +3028,7 @@
         <v>5.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK13" t="n">
         <v>1.85</v>
@@ -3404,7 +3404,7 @@
         <v>1.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AE15" t="n">
         <v>1.85</v>
@@ -3425,10 +3425,10 @@
         <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AM15" t="n">
         <v>1.3</v>
@@ -3479,16 +3479,16 @@
         <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="BD15" t="n">
         <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2180,28 +2180,28 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
         <v>2.7</v>
@@ -2210,13 +2210,13 @@
         <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
         <v>1.3</v>
@@ -2225,34 +2225,34 @@
         <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="BC9" t="n">
         <v>2.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
         <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="V12" t="n">
         <v>1.36</v>
@@ -2795,13 +2795,13 @@
         <v>2.88</v>
       </c>
       <c r="X12" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.09</v>
@@ -2840,10 +2840,10 @@
         <v>2</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>5.76</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="R3" t="n">
-        <v>4.33</v>
+        <v>5.76</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>4.53</v>
       </c>
       <c r="R9" t="n">
         <v>5.2</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AB9" t="n">
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.15</v>
+        <v>4.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2998,7 +2998,7 @@
         <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AA13" t="n">
         <v>1.1</v>
@@ -3016,7 +3016,7 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
         <v>2.9</v>
@@ -3025,10 +3025,10 @@
         <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK13" t="n">
         <v>1.85</v>
@@ -3189,7 +3189,7 @@
         <v>2.6</v>
       </c>
       <c r="X14" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="Y14" t="n">
         <v>1.33</v>
@@ -3204,16 +3204,16 @@
         <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AE14" t="n">
         <v>2.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
         <v>3.8</v>
@@ -3380,13 +3380,13 @@
         <v>4.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="X15" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="Y15" t="n">
         <v>1.42</v>
@@ -3395,7 +3395,7 @@
         <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
@@ -3404,7 +3404,7 @@
         <v>1.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AE15" t="n">
         <v>1.85</v>
@@ -3422,7 +3422,7 @@
         <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
         <v>1.73</v>
@@ -3479,16 +3479,16 @@
         <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
         <v>3.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1007,7 +1007,7 @@
         <v>5.76</v>
       </c>
       <c r="S3" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
         <v>2.38</v>
@@ -1040,7 +1040,7 @@
         <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AE3" t="n">
         <v>1.92</v>
@@ -1049,16 +1049,16 @@
         <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK3" t="n">
         <v>1.85</v>
@@ -1121,7 +1121,7 @@
         <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BF3" t="n">
         <v>1.17</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2180,16 +2180,16 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.53</v>
+        <v>4.15</v>
       </c>
       <c r="R9" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="T9" t="n">
         <v>2.4</v>
@@ -2219,13 +2219,13 @@
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF9" t="n">
         <v>2.1</v>
@@ -2234,10 +2234,10 @@
         <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.12</v>
@@ -2246,7 +2246,7 @@
         <v>1.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AM9" t="n">
         <v>1.2</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="BD9" t="n">
         <v>4.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
@@ -2792,16 +2792,16 @@
         <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
         <v>1.09</v>
@@ -2828,16 +2828,16 @@
         <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
         <v>1.33</v>
@@ -3010,25 +3010,25 @@
         <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF13" t="n">
         <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
         <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK13" t="n">
         <v>1.85</v>
@@ -3207,16 +3207,16 @@
         <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AF14" t="n">
         <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AH14" t="n">
         <v>1.22</v>
@@ -3282,16 +3282,16 @@
         <v>1.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BE14" t="n">
         <v>1.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3374,28 +3374,28 @@
         <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="X15" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="Y15" t="n">
         <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB15" t="n">
         <v>1.02</v>
@@ -3422,16 +3422,16 @@
         <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
         <v>1.73</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AN15" t="n">
         <v>1.78</v>
@@ -3482,7 +3482,7 @@
         <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
         <v>1.65</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
         <v>4.05</v>
       </c>
       <c r="R3" t="n">
-        <v>5.76</v>
+        <v>5.9</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1016,7 +1016,7 @@
         <v>5.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>3</v>
@@ -1040,7 +1040,7 @@
         <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AE3" t="n">
         <v>1.92</v>
@@ -1049,19 +1049,19 @@
         <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
         <v>1.85</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
         <v>1.95</v>
@@ -1124,7 +1124,7 @@
         <v>1.73</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S4" t="n">
         <v>2.9</v>
@@ -1225,10 +1225,10 @@
         <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
         <v>1.13</v>
@@ -1252,10 +1252,10 @@
         <v>1.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
         <v>2.23</v>
@@ -1273,40 +1273,40 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB4" t="n">
         <v>1.4</v>
@@ -1321,7 +1321,7 @@
         <v>1.32</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="R11" t="n">
-        <v>5.43</v>
+        <v>5.15</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI15"/>
+  <dimension ref="A1:BI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46106.72916666666</v>
+        <v>46106.66666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46106.83333333334</v>
+        <v>46106.72916666666</v>
       </c>
     </row>
     <row r="10">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="R10" t="n">
-        <v>5.43</v>
+        <v>5.15</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="X10" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>5.15</v>
+        <v>5.43</v>
       </c>
       <c r="S11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.95</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AL11" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46106.85416666666</v>
+        <v>46106.83333333334</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.64</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.45</v>
+        <v>3.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>5.17</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="X13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB13" t="n">
         <v>1.02</v>
       </c>
       <c r="AC13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46106.875</v>
+        <v>46106.85416666666</v>
       </c>
     </row>
     <row r="14">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>4.75</v>
+        <v>5.17</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="V14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.44</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.81</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AN14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AM14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46106.91666666666</v>
+        <v>46106.875</v>
       </c>
     </row>
     <row r="15">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,141 +3362,338 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" s="3" t="n">
+        <v>46106.91666666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" t="n">
         <v>3.05</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>3.06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>2.63</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>2.2</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>3.8</v>
       </c>
-      <c r="V15" t="n">
+      <c r="V16" t="n">
         <v>1.36</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>2.9</v>
       </c>
-      <c r="X15" t="n">
+      <c r="X16" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y16" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z16" t="n">
         <v>6.5</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AA16" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AB16" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC16" t="n">
         <v>1.29</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD16" t="n">
         <v>3.4</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AG16" t="n">
         <v>3</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AH16" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AI16" t="n">
         <v>5.5</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AJ16" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AK16" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AL16" t="n">
         <v>2.01</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AM16" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AN16" t="n">
         <v>1.78</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.25</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BC16" t="n">
         <v>2.1</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BD16" t="n">
         <v>3.6</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BE16" t="n">
         <v>1.65</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BF16" t="n">
         <v>1.18</v>
       </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI15" s="3" t="n">
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="3" t="n">
         <v>46106.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>4.35</v>
+        <v>3.98</v>
       </c>
       <c r="V4" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
         <v>11</v>
@@ -1231,22 +1231,22 @@
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="n">
         <v>1.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="AH4" t="n">
         <v>1.1</v>
@@ -1258,70 +1258,70 @@
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AM4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.33</v>
       </c>
-      <c r="AN4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.32</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1392,28 +1392,28 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
         <v>3.6</v>
@@ -1437,7 +1437,7 @@
         <v>2.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
         <v>1.48</v>
@@ -1455,55 +1455,55 @@
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB5" t="n">
         <v>1.38</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>5.43</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.42</v>
+        <v>4.05</v>
       </c>
       <c r="R2" t="n">
-        <v>4.35</v>
+        <v>5.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>5.9</v>
+        <v>4.33</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.15</v>
+        <v>3.78</v>
       </c>
       <c r="R10" t="n">
-        <v>5.15</v>
+        <v>5.41</v>
       </c>
       <c r="S10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG10" t="n">
         <v>3.2</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.65</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL10" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AM10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>5.43</v>
+        <v>8.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>5.8</v>
+        <v>7.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,28 +2968,28 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>2.15</v>
       </c>
       <c r="U13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="X13" t="n">
         <v>2.62</v>
@@ -2998,7 +2998,7 @@
         <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
         <v>1.09</v>
@@ -3013,34 +3013,34 @@
         <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AH13" t="n">
         <v>1.3</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>5.64</v>
+        <v>4.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
         <v>2.38</v>
@@ -3189,13 +3189,13 @@
         <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA14" t="n">
         <v>1.1</v>
@@ -3207,16 +3207,16 @@
         <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH14" t="n">
         <v>1.36</v>
@@ -3228,10 +3228,10 @@
         <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AM14" t="n">
         <v>1.22</v>
@@ -3282,7 +3282,7 @@
         <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="BD14" t="n">
         <v>3.8</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S15" t="n">
         <v>4.75</v>
@@ -3386,7 +3386,7 @@
         <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
@@ -3401,19 +3401,19 @@
         <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AE15" t="n">
         <v>2.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AH15" t="n">
         <v>1.22</v>
@@ -3425,13 +3425,13 @@
         <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>1.73</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN15" t="n">
         <v>1.22</v>
@@ -3482,13 +3482,13 @@
         <v>2.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,22 +3559,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="R16" t="n">
-        <v>3.06</v>
+        <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T16" t="n">
         <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="V16" t="n">
         <v>1.36</v>
@@ -3583,13 +3583,13 @@
         <v>2.9</v>
       </c>
       <c r="X16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.09</v>
@@ -3598,16 +3598,16 @@
         <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
         <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3622,16 +3622,16 @@
         <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3676,13 +3676,13 @@
         <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="BD16" t="n">
         <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="BF16" t="n">
         <v>1.18</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>5.9</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
         <v>1.73</v>
@@ -1240,7 +1240,7 @@
         <v>2.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AF4" t="n">
         <v>1.34</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AQ4" t="n">
         <v>2.21</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>4.27</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.75</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>5.25</v>
+        <v>2.41</v>
       </c>
       <c r="V5" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AN5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.88</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="V7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W7" t="n">
-        <v>2.79</v>
+        <v>2.47</v>
       </c>
       <c r="X7" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.4</v>
+        <v>9.1</v>
       </c>
       <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>6.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.88</v>
       </c>
       <c r="R8" t="n">
-        <v>3.06</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>6.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="U8" t="n">
-        <v>4.01</v>
+        <v>2.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.47</v>
+        <v>2.79</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.55</v>
+        <v>1.05</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.41</v>
+        <v>1.98</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.72</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,37 +2377,37 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>5.41</v>
+        <v>8.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>5.25</v>
+        <v>7.9</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="AA10" t="n">
         <v>1.08</v>
@@ -2416,40 +2416,40 @@
         <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,37 +2771,37 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3.76</v>
       </c>
       <c r="R12" t="n">
-        <v>8.6</v>
+        <v>5.35</v>
       </c>
       <c r="S12" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="AA12" t="n">
         <v>1.08</v>
@@ -2810,94 +2810,94 @@
         <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>3.3</v>
@@ -2998,7 +2998,7 @@
         <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
         <v>1.09</v>
@@ -3013,13 +3013,13 @@
         <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.14</v>
+        <v>2.83</v>
       </c>
       <c r="AH13" t="n">
         <v>1.3</v>
@@ -3034,7 +3034,7 @@
         <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AM13" t="n">
         <v>1.3</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1792,22 +1792,22 @@
         <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
         <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
         <v>3.28</v>
@@ -1825,10 +1825,10 @@
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE7" t="n">
         <v>2.35</v>
@@ -1843,22 +1843,22 @@
         <v>1.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AM7" t="n">
         <v>1.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R10" t="n">
         <v>5</v>
       </c>
-      <c r="R10" t="n">
-        <v>8.6</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.32</v>
+        <v>1.7</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.97</v>
+        <v>2.27</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BD11" t="n">
         <v>4.2</v>
       </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK11" t="n">
+      <c r="BE11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.27</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73</v>
+        <v>4.39</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>2.65</v>
       </c>
       <c r="T5" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>2.41</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>4.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>4.39</v>
+        <v>1.73</v>
       </c>
       <c r="S6" t="n">
-        <v>2.65</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>5.25</v>
+        <v>2.41</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="X6" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AN6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>4.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>4.06</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.46</v>
+        <v>3.01</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>2.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD7" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.41</v>
+        <v>1.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="S10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
         <v>5.25</v>
       </c>
       <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.29</v>
       </c>
-      <c r="W10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="R11" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="S11" t="n">
         <v>1.79</v>
@@ -2598,10 +2598,10 @@
         <v>2.97</v>
       </c>
       <c r="X11" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
         <v>6.1</v>
@@ -2610,22 +2610,22 @@
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
         <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AH11" t="n">
         <v>1.32</v>
@@ -2637,10 +2637,10 @@
         <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AM11" t="n">
         <v>1.12</v>
@@ -2652,40 +2652,40 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="BB11" t="n">
         <v>1.19</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="BF12" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
         <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
@@ -3019,7 +3019,7 @@
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AH13" t="n">
         <v>1.3</v>
@@ -3046,40 +3046,40 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BB13" t="n">
         <v>1.25</v>
@@ -3165,16 +3165,16 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
         <v>2.38</v>
@@ -3228,10 +3228,10 @@
         <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AM14" t="n">
         <v>1.22</v>
@@ -3243,46 +3243,46 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB14" t="n">
         <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>3.8</v>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.95</v>
+        <v>4.54</v>
       </c>
       <c r="Q15" t="n">
         <v>3.4</v>
@@ -3404,7 +3404,7 @@
         <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AE15" t="n">
         <v>2.12</v>
@@ -3428,10 +3428,10 @@
         <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
         <v>1.22</v>
@@ -3440,40 +3440,40 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB15" t="n">
         <v>1.3</v>
@@ -3485,7 +3485,7 @@
         <v>3.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BF15" t="n">
         <v>1.12</v>
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
         <v>3.95</v>
       </c>
       <c r="S16" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T16" t="n">
         <v>2.2</v>
@@ -3601,13 +3601,13 @@
         <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AE16" t="n">
         <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3625,10 +3625,10 @@
         <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AN16" t="n">
         <v>1.83</v>
@@ -3637,52 +3637,52 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB16" t="n">
         <v>1.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="BD16" t="n">
         <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BF16" t="n">
         <v>1.18</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="S3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="V4" t="n">
         <v>1.73</v>
@@ -1258,16 +1258,16 @@
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AR4" t="n">
         <v>3.08</v>
@@ -1291,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AW4" t="n">
         <v>1.28</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>4.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.92</v>
+        <v>3.24</v>
       </c>
       <c r="R5" t="n">
-        <v>4.39</v>
+        <v>1.76</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>5.25</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="X5" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.74</v>
+        <v>1.12</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.51</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.27</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.73</v>
       </c>
-      <c r="S6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AR6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.37</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>3.22</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>2.94</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>4.19</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>3.01</v>
+        <v>2.39</v>
       </c>
       <c r="X7" t="n">
-        <v>2.53</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>4.37</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3.22</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="T8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1.88</v>
       </c>
-      <c r="U8" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="BF10" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.55</v>
+        <v>3.78</v>
       </c>
       <c r="R11" t="n">
-        <v>8.27</v>
+        <v>4.86</v>
       </c>
       <c r="S11" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BA11" t="n">
-        <v>6.86</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="R12" t="n">
-        <v>4.95</v>
+        <v>8.27</v>
       </c>
       <c r="S12" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>5.25</v>
+        <v>7.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.54</v>
+        <v>6.86</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="R10" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="S10" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
         <v>5.25</v>
       </c>
       <c r="V10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.29</v>
       </c>
-      <c r="W10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE10" t="n">
+      <c r="AI10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.78</v>
+        <v>4.55</v>
       </c>
       <c r="R11" t="n">
-        <v>4.86</v>
+        <v>8.27</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>5.25</v>
+        <v>7.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.67</v>
+        <v>3.48</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.97</v>
+        <v>3.86</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.28</v>
+        <v>5.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>6.86</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>8.27</v>
+        <v>4.95</v>
       </c>
       <c r="S12" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.48</v>
+        <v>2.07</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.95</v>
+        <v>3.82</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AX12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.17</v>
       </c>
-      <c r="AY12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC12" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>4.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>4.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>4.75</v>
+        <v>2.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="X6" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.51</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>8.27</v>
+        <v>4.95</v>
       </c>
       <c r="S11" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.04</v>
+        <v>1.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.48</v>
+        <v>2.07</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.86</v>
+        <v>2.72</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.95</v>
+        <v>3.82</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.7</v>
+        <v>2.09</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AX11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.17</v>
       </c>
-      <c r="AY11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="R12" t="n">
-        <v>4.95</v>
+        <v>8.27</v>
       </c>
       <c r="S12" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>5.25</v>
+        <v>7.9</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.54</v>
+        <v>6.86</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,112 +801,112 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>2.93</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>2.37</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>4.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>4.75</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="X5" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.37</v>
+        <v>2.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.51</v>
       </c>
-      <c r="AX5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.69</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>2.42</v>
+        <v>4.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.37</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>3.22</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>2.94</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>4.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>3.01</v>
+        <v>2.39</v>
       </c>
       <c r="X8" t="n">
-        <v>2.53</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>4.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>3.22</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="T9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL9" t="n">
         <v>1.88</v>
       </c>
-      <c r="U9" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="S10" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
         <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="BF10" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>4.95</v>
+        <v>7.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U11" t="n">
-        <v>5.25</v>
+        <v>6.7</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
         <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>8.27</v>
+        <v>4.35</v>
       </c>
       <c r="S12" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>7.9</v>
+        <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" t="n">
         <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.95</v>
+        <v>5.17</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.86</v>
+        <v>6.71</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="S13" t="n">
         <v>3.3</v>
@@ -3013,13 +3013,13 @@
         <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
         <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AH13" t="n">
         <v>1.3</v>
@@ -3034,7 +3034,7 @@
         <v>1.73</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM13" t="n">
         <v>1.3</v>
@@ -3046,16 +3046,16 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AT13" t="n">
         <v>3.84</v>
@@ -3064,22 +3064,22 @@
         <v>2.83</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AW13" t="n">
         <v>1.68</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="BB13" t="n">
         <v>1.25</v>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
         <v>4.2</v>
@@ -3189,7 +3189,7 @@
         <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
         <v>1.48</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.54</v>
+        <v>3.68</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="S15" t="n">
         <v>4.75</v>
@@ -3386,7 +3386,7 @@
         <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
@@ -3407,7 +3407,7 @@
         <v>2.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AF15" t="n">
         <v>1.65</v>
@@ -3425,10 +3425,10 @@
         <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AM15" t="n">
         <v>1.3</v>
@@ -3559,16 +3559,16 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
         <v>2.2</v>
@@ -3589,7 +3589,7 @@
         <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="AA16" t="n">
         <v>1.09</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -790,14 +790,14 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -987,24 +987,24 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -1043,7 +1043,7 @@
         <v>3.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
         <v>2</v>
@@ -1169,13 +1169,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1184,24 +1184,24 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>3.6</v>
@@ -1210,7 +1210,7 @@
         <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>3.84</v>
+        <v>4.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.73</v>
@@ -1240,7 +1240,7 @@
         <v>2.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AF4" t="n">
         <v>1.34</v>
@@ -1276,7 +1276,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AR4" t="n">
         <v>3.08</v>
@@ -1288,13 +1288,13 @@
         <v>7.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AV4" t="n">
         <v>1.58</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AX4" t="n">
         <v>1.12</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1388,137 +1388,137 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.69</v>
+        <v>1.94</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.24</v>
+        <v>2.87</v>
       </c>
       <c r="R5" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
-        <v>2.42</v>
+        <v>4.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.78</v>
+        <v>2.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1585,137 +1585,137 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT6" t="n">
         <v>4</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AU6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.46</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="BB6" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="S8" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
         <v>1.02</v>
@@ -2022,37 +2022,37 @@
         <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
         <v>4.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
         <v>2.02</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
         <v>1.47</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF8" t="n">
         <v>1.09</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.37</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5.42</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="V9" t="n">
         <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AI9" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R10" t="n">
-        <v>4.95</v>
+        <v>7.75</v>
       </c>
       <c r="S10" t="n">
-        <v>2.03</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
-        <v>5.25</v>
+        <v>6.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>7.75</v>
+        <v>4.35</v>
       </c>
       <c r="S11" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>6.7</v>
+        <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.86</v>
+        <v>3.45</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.95</v>
+        <v>5.17</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AW11" t="n">
         <v>1.45</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.86</v>
+        <v>6.71</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>4.35</v>
+        <v>4.95</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
         <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="BF12" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -1366,13 +1366,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1381,14 +1381,14 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.72</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.55</v>
       </c>
-      <c r="S7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V7" t="n">
+      <c r="AG7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.3</v>
       </c>
-      <c r="W7" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AN7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC7" t="n">
         <v>2.41</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="BD7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.46</v>
       </c>
-      <c r="Z7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="BF7" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,80 +1983,80 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>4.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>5.4</v>
       </c>
       <c r="T8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.87</v>
       </c>
-      <c r="U8" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AL8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN8" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.41</v>
+        <v>1.84</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.14</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.46</v>
+        <v>1.84</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>4.35</v>
+        <v>4.95</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="BF11" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>4.95</v>
+        <v>4.35</v>
       </c>
       <c r="S12" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
         <v>5.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG12" t="n">
         <v>3.3</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF12" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>

--- a/jogos_2026-03-25.xlsx
+++ b/jogos_2026-03-25.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -790,144 +790,144 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R2" t="n">
         <v>7</v>
       </c>
-      <c r="N2" t="n">
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4</v>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -998,112 +998,112 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.4</v>
+        <v>2.93</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.81</v>
+        <v>2.37</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1748,19 +1748,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1769,96 +1769,96 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>6.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>6.27</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>4.08</v>
+        <v>1.98</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>2.97</v>
       </c>
       <c r="X7" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.62</v>
+        <v>3.94</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.2</v>
+        <v>2.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.1</v>
+        <v>4.65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.3</v>
+        <v>2.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,96 +1945,96 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="S8" t="n">
         <v>4.72</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.4</v>
-      </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>3.04</v>
+        <v>2.53</v>
       </c>
       <c r="X8" t="n">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="AH8" t="n">
         <v>1.37</v>
@@ -2043,73 +2043,73 @@
         <v>4.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC8" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,19 +2142,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2166,147 +2166,147 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>5.42</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC9" t="n">
         <v>2.41</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>7.75</v>
+        <v>4.95</v>
       </c>
       <c r="S10" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="T10" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>6.7</v>
+        <v>5.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.48</v>
+        <v>2.02</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.86</v>
+        <v>2.63</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.95</v>
+        <v>3.66</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.45</v>
+        <v>2.92</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AX10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.17</v>
       </c>
-      <c r="AY10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC10" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>4.95</v>
+        <v>4.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
         <v>5.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
         <v>3.3</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AF11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>4.35</v>
+        <v>7.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>5.25</v>
+        <v>6.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA12" t="n">
         <v>1.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.38</v>
+        <v>2.97</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.17</v>
+        <v>5.95</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AW12" t="n">
         <v>1.45</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.71</v>
+        <v>6.86</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
